--- a/cypress/fixtures/PTAXEXTRACT.xlsx
+++ b/cypress/fixtures/PTAXEXTRACT.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="56">
   <si>
     <t>Total property tax demand (including cess, other taxes, AND excluding user charges if user charges are collected with property tax) Question 1.9</t>
   </si>
@@ -56,6 +56,172 @@
   </si>
   <si>
     <t>Yes</t>
+  </si>
+  <si>
+    <t>Testing</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 
+Total property tax collection(1.17)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 
+Current property tax collection(1.18)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 
+Arrear property tax collection(1.19)</t>
+  </si>
+  <si>
+    <t>Total property tax collection (excluding cess,other taxes, user charges if any)1.20</t>
+  </si>
+  <si>
+    <t>Other tax collections (Collection figure for each type of tax other than property tax collected 1.21.1</t>
+  </si>
+  <si>
+    <t>Cess collection (Collection figure for each type of cess collected
+1.22.1</t>
+  </si>
+  <si>
+    <t>Total number of properties mapped in the ULB (including properties exempted from paying property tax) *2.1</t>
+  </si>
+  <si>
+    <t>Total number of properties exempted from paying property tax 2.2</t>
+  </si>
+  <si>
+    <t>Total number of properties from which property tax was demanded *2.3</t>
+  </si>
+  <si>
+    <t>Total number of properties from which property tax was collected2.4</t>
+  </si>
+  <si>
+    <t>Number of properties from which property tax was demanded *2.6</t>
+  </si>
+  <si>
+    <t>Value of property tax demanded (INR lakhs) * 2.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Value of property tax collected (INR lakhs) *
+2.7
+</t>
+  </si>
+  <si>
+    <t>Number of properties from which property tax was collected *
+2.8</t>
+  </si>
+  <si>
+    <t>Value of property tax demanded (INR lakhs) * 2.9</t>
+  </si>
+  <si>
+    <t>Number of properties from which property tax was demanded * 2.10</t>
+  </si>
+  <si>
+    <t>Value of property tax collected (INR lakhs) * 2.11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of properties from which property tax was collected *
+2.12
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 
+Value of property tax demanded (INR lakhs) * 2.13</t>
+  </si>
+  <si>
+    <t>Number of properties from which property tax was demanded * 2.14</t>
+  </si>
+  <si>
+    <t>Value of property tax collected (INR lakhs) * 2.15</t>
+  </si>
+  <si>
+    <t>Number of properties from which property tax was collected * 2.16</t>
+  </si>
+  <si>
+    <t>alue of property tax demanded (INR lakhs) * 2.17</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 
+Number of properties from which property tax was demanded * 2.18</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 
+Value of property tax collected (INR lakhs) *
+2.19</t>
+  </si>
+  <si>
+    <t>Number of properties from which property tax was collected * 2.20</t>
+  </si>
+  <si>
+    <t>Value of property tax demanded (INR lakhs) * 2.21</t>
+  </si>
+  <si>
+    <t>Number of properties from which property tax was demanded * 2.22</t>
+  </si>
+  <si>
+    <t>Value of property tax collected (INR lakhs) * 2.23</t>
+  </si>
+  <si>
+    <t>Number of properties from which property tax was collected * 2.24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9556.00
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">228287
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">227667
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3763
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">147
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 
+Value of property tax demanded (INR lakhs) (1) 2.26.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Number of properties from which property tax was demanded   2.27.1 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 
+Value of property tax collected (INR lakhs) (1)  2.28.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 
+Number of properties from which property tax was collected (1) 2.29.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 
+Number of properties that paid online (through website or mobile application) 3.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Total collections made via online channel i.e. through website or mobile application (INR lakhs) 3.2 </t>
   </si>
 </sst>
 </file>
@@ -376,16 +542,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:AS8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.140625" customWidth="1"/>
     <col min="2" max="3" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.140625" customWidth="1"/>
     <col min="6" max="6" width="9" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="240" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:45" s="1" customFormat="1" ht="255" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -413,29 +581,254 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="J1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AK1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AL1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AN1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AO1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="AP1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="AQ1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="AS1" s="1" t="s">
+        <v>55</v>
+      </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>50</v>
+    <row r="2" spans="1:45" ht="30" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="B2">
-        <v>25</v>
+        <v>6311</v>
       </c>
       <c r="C2">
-        <v>25</v>
+        <v>3245</v>
       </c>
       <c r="D2">
         <v>20</v>
       </c>
+      <c r="E2" s="1" t="s">
+        <v>41</v>
+      </c>
       <c r="F2">
-        <v>20</v>
+        <v>0</v>
+      </c>
+      <c r="G2" t="s">
+        <v>10</v>
       </c>
       <c r="H2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I2" t="s">
         <v>9</v>
       </c>
+      <c r="J2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="K2">
+        <v>6311</v>
+      </c>
+      <c r="L2">
+        <v>3245</v>
+      </c>
+      <c r="M2">
+        <v>9556</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q2">
+        <v>620</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="S2">
+        <v>164947</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="U2">
+        <v>198297</v>
+      </c>
+      <c r="V2">
+        <v>3763</v>
+      </c>
+      <c r="W2">
+        <v>140147</v>
+      </c>
+      <c r="X2">
+        <v>5636</v>
+      </c>
+      <c r="Y2">
+        <v>29324</v>
+      </c>
+      <c r="Z2">
+        <v>5636</v>
+      </c>
+      <c r="AA2">
+        <v>24754</v>
+      </c>
+      <c r="AB2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AC2">
+        <v>1</v>
+      </c>
+      <c r="AD2">
+        <v>8</v>
+      </c>
+      <c r="AE2">
+        <v>1</v>
+      </c>
+      <c r="AF2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AG2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AH2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AI2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AJ2">
+        <v>16</v>
+      </c>
+      <c r="AK2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AL2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AM2">
+        <v>2</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>0</v>
+      </c>
+      <c r="AP2">
+        <v>0</v>
+      </c>
+      <c r="AQ2">
+        <v>0</v>
+      </c>
+      <c r="AR2">
+        <v>234</v>
+      </c>
+      <c r="AS2">
+        <v>6776</v>
+      </c>
+    </row>
+    <row r="8" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="D8" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
